--- a/public/providers_template.xlsx
+++ b/public/providers_template.xlsx
@@ -534,10 +534,10 @@
         <v>80</v>
       </c>
       <c r="L2" t="str">
-        <v>05xxxxxxxx</v>
+        <v>0500000000</v>
       </c>
       <c r="M2" t="str">
-        <v>9665xxxxxxxx</v>
+        <v>966500000001</v>
       </c>
       <c r="N2" t="str">
         <v/>
